--- a/survey_templates/050_email_communication_survey--survey_templates.xlsx
+++ b/survey_templates/050_email_communication_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Open rate</t>
+          <t>What is your open rate (as a percentage)?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>email_click_rate</t>
+          <t>email_open_rate_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Click rate</t>
+          <t>What is the open rate of your emails?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,63 +607,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>email_reply_rate</t>
+          <t>email_target_audience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reply rate</t>
+          <t>What is the target audience for your emails?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email_open_rate_1</t>
+          <t>email_body</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Open rate 1</t>
+          <t>What is the content of your email body like?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email_click_rate_1</t>
+          <t>email_call_to_action</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Click rate 1</t>
+          <t>Do you have a call to action in your emails?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email_reply_rate_1</t>
+          <t>email_target_audience_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reply rate 1</t>
+          <t>Email Target Audience 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email_subject_lines</t>
+          <t>email_click_rate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email subject line</t>
+          <t>What is your click rate (as a percentage)?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,58 +727,58 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email_body</t>
+          <t>email_reply_rate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Email body</t>
+          <t>What is your reply rate (as a percentage)?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email_call_to_action</t>
+          <t>email_reply_rate_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Call to action</t>
+          <t>What is the reply rate of your emails?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email_target_audience</t>
+          <t>email_frequency_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Target audience</t>
+          <t>How often do you send emails?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,46 +791,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email_frequency_3</t>
+          <t>email_subject</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How often?</t>
+          <t>What is your email subject line like?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email_frequency_2</t>
+          <t>email_click_rate_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How often do you?</t>
+          <t>What is the click rate of your emails?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>email_open_rate_2</t>
+          <t>email_body_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Open rate</t>
+          <t>Email Body 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,225 +865,64 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email_target_audience_2</t>
+          <t>email_target_audience_2_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Target audience</t>
+          <t>Email Target Audience 2 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>email_body_2</t>
+          <t>email_frequency_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email body</t>
+          <t>How often do you interact with emails?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email_target_audience_3</t>
+          <t>email_reply_rate_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Target audience</t>
+          <t>Email Reply Rate 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>email_frequency_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How often?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>email_open_rate_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Open rate</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>email_click_rate_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Click rate</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>email_reply_rate_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Reply rate</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>email_reply_rate_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Reply rate 2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>email_target_audience_1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Target audience 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>email_target_audience_4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Target audience 2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1148,80 +987,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>email_call_to_action_choices</t>
+          <t>email_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>email_call_to_action_choices</t>
+          <t>email_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>email_target_audience_choices</t>
+          <t>email_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'email'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Email'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>email_target_audience_choices</t>
+          <t>email_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'social_media'}</t>
+          <t>less_than_1/month</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Social media'}</t>
+          <t>Less than 1/month</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'phone'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Phone'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'text_message'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Text message'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1284,182 +1123,182 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'website'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Website'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>email_frequency_3_choices</t>
+          <t>email_target_audience_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'daily'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Daily'}</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>email_frequency_3_choices</t>
+          <t>email_target_audience_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'weekly'}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'Weekly'}</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>email_frequency_3_choices</t>
+          <t>email_call_to_action_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'monthly'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Monthly'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>email_frequency_3_choices</t>
+          <t>email_call_to_action_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'quarterly'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'Quarterly'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>email_frequency_3_choices</t>
+          <t>email_target_audience_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'annually'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'Annually'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>email_frequency_3_choices</t>
+          <t>email_target_audience_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'less_than_1/month'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'Less than 1/month'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>email_frequency_2_choices</t>
+          <t>email_target_audience_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_'daily'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': 'Daily'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>email_frequency_2_choices</t>
+          <t>email_target_audience_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_'weekly'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': 'Weekly'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>email_frequency_2_choices</t>
+          <t>email_target_audience_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_'monthly'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': 'Monthly'}</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>email_frequency_2_choices</t>
+          <t>email_target_audience_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option':_'quarterly'}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option': 'Quarterly'}</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option':_'annually'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option': 'Annually'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1488,522 +1327,284 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option':_'less_than_1/month'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option': 'Less than 1/month'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>email_target_audience_2_choices</t>
+          <t>email_frequency_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option':_'email'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option': 'Email'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>email_target_audience_2_choices</t>
+          <t>email_frequency_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option':_'social_media'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option': 'Social media'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>email_target_audience_2_choices</t>
+          <t>email_frequency_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option':_'phone'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option': 'Phone'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>email_target_audience_2_choices</t>
+          <t>email_frequency_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>less_than_1/month</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Less than 1/month</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>email_target_audience_2_choices</t>
+          <t>email_target_audience_2_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option':_'text_message'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option': 'Text message'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>email_target_audience_2_choices</t>
+          <t>email_target_audience_2_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option':_'website'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option': 'Website'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>email_target_audience_3_choices</t>
+          <t>email_target_audience_2_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option':_'email'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option': 'Email'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>email_target_audience_3_choices</t>
+          <t>email_target_audience_2_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option':_'social_media'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option': 'Social media'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>email_target_audience_3_choices</t>
+          <t>email_target_audience_2_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option':_'phone'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option': 'Phone'}</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>email_target_audience_3_choices</t>
+          <t>email_target_audience_2_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>email_target_audience_3_choices</t>
+          <t>email_frequency_3_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'option':_'text_message'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'option': 'Text message'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>email_target_audience_3_choices</t>
+          <t>email_frequency_3_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'option':_'website'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'option': 'Website'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>email_frequency_4_choices</t>
+          <t>email_frequency_3_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'option':_'daily'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'option': 'Daily'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>email_frequency_4_choices</t>
+          <t>email_frequency_3_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'option':_'weekly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'option': 'Weekly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>email_frequency_4_choices</t>
+          <t>email_frequency_3_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'option':_'monthly'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'option': 'Monthly'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>email_frequency_4_choices</t>
+          <t>email_frequency_3_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'option':_'quarterly'}</t>
+          <t>less_than_1/month</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'option': 'Quarterly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>email_frequency_4_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'option':_'annually'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'option': 'Annually'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>email_frequency_4_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'option':_'less_than_1/month'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'option': 'Less than 1/month'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>email_target_audience_1_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'option':_'email'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'option': 'Email'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>email_target_audience_1_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'option':_'social_media'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'option': 'Social media'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>email_target_audience_1_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'option':_'phone'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'option': 'Phone'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>email_target_audience_1_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'option':_'other'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'option': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>email_target_audience_1_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'option':_'text_message'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'option': 'Text message'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>email_target_audience_1_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'option':_'website'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'option': 'Website'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>email_target_audience_4_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'option':_'email'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'option': 'Email'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>email_target_audience_4_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'option':_'social_media'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'option': 'Social media'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>email_target_audience_4_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'option':_'phone'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'option': 'Phone'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>email_target_audience_4_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'option':_'other'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'option': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>email_target_audience_4_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'option':_'text_message'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'option': 'Text message'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>email_target_audience_4_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'option':_'website'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'option': 'Website'}</t>
+          <t>Less than 1/month</t>
         </is>
       </c>
     </row>
